--- a/docs/thong_tin_giam_dinh_xe.xlsx
+++ b/docs/thong_tin_giam_dinh_xe.xlsx
@@ -697,7 +697,11 @@
           <t>Giấy phép lưu hành</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>VA 3365650</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="8">
       <c r="A15" s="2" t="inlineStr">
@@ -1038,7 +1042,11 @@
           <t>Số hồ sơ</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="8">
       <c r="A38" s="2" t="inlineStr">
@@ -1051,7 +1059,11 @@
           <t>Mã giám định viên</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="8">
       <c r="A39" s="2" t="inlineStr">
@@ -1081,7 +1093,11 @@
           <t>Ngày giám định</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="8">
       <c r="A41" s="2" t="inlineStr">
@@ -1094,7 +1110,11 @@
           <t>Ngày vào gara</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1" s="8">
       <c r="A42" s="7" t="inlineStr">
@@ -1131,7 +1151,11 @@
           <t>Giờ tai nạn</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="8">
       <c r="A45" s="2" t="inlineStr">
@@ -1144,7 +1168,11 @@
           <t>Địa điểm tai nạn</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="8">
       <c r="A46" s="2" t="inlineStr">
@@ -1157,7 +1185,11 @@
           <t>Diễn biến tai nạn</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="8">
       <c r="A47" s="2" t="inlineStr">
@@ -1170,7 +1202,11 @@
           <t>Nguyên nhân</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1" s="8">
       <c r="A48" s="7" t="inlineStr">
@@ -1190,7 +1226,11 @@
           <t>Ngày hóa đơn</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="8">
       <c r="A50" s="2" t="inlineStr">
@@ -1203,7 +1243,11 @@
           <t>Tháng hóa đơn</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="8">
       <c r="A51" s="2" t="inlineStr">
@@ -1216,7 +1260,11 @@
           <t>Năm hóa đơn</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="8">
       <c r="A52" s="2" t="inlineStr">
@@ -1229,7 +1277,11 @@
           <t>Tổng cộng tiền thanh toán</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1" s="8">
       <c r="A53" s="7" t="inlineStr">
@@ -1249,7 +1301,11 @@
           <t>Tên gara</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="8">
       <c r="A55" s="2" t="inlineStr">
@@ -1262,7 +1318,11 @@
           <t>Số tài khoản</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="8">
       <c r="A56" s="2" t="inlineStr">
@@ -1275,7 +1335,11 @@
           <t>Tên ngân hàng</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr"/>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="8">
       <c r="A57" s="2" t="inlineStr">
@@ -1288,7 +1352,11 @@
           <t>Địa chỉ ngân hàng</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr"/>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
     </row>
     <row r="58"/>
     <row r="59">

--- a/docs/thong_tin_giam_dinh_xe.xlsx
+++ b/docs/thong_tin_giam_dinh_xe.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
@@ -1283,39 +1283,39 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1" s="8">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="53" ht="18" customHeight="1" s="8">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>{tien_tt}</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Tiền thanh toán</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="8">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>H. GARA SỬA CHỮA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1" s="8">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>{ten_gara}</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Tên gara</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>...</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="8">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>{so_tk}</t>
+          <t>{ten_gara}</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Số tài khoản</t>
+          <t>Tên gara</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="56" ht="18" customHeight="1" s="8">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>{ten_ngan_hang}</t>
+          <t>{so_tk}</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Tên ngân hàng</t>
+          <t>Số tài khoản</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1344,23 +1344,40 @@
     <row r="57" ht="18" customHeight="1" s="8">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>{ten_ngan_hang}</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Tên ngân hàng</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>{dia_chi_ngan_hang}</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Địa chỉ ngân hàng</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>💡 Chỉ điền vào cột C (Giá trị). Không thay đổi cột A và B.</t>
         </is>
@@ -1369,14 +1386,14 @@
   </sheetData>
   <autoFilter ref="A1:C57"/>
   <mergeCells count="8">
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A54:C54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
